--- a/Output/summary_OMOP_vocabs_study_merge.xlsx
+++ b/Output/summary_OMOP_vocabs_study_merge.xlsx
@@ -31746,7 +31746,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:M11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -31757,30 +31757,60 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>hararghe_hdss_cdm_Non-Standard but Valid</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
           <t>hararghe_hdss_cdm_Standard</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>igangamayuge_hdss_cdm_Non-Standard but Valid</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>igangamayuge_hdss_cdm_Standard</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>meiru_karonga_hdss_cdm_Non-Standard but Valid</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>meiru_karonga_hdss_cdm_Standard</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>niakhar_hdss_cdm_Non-Standard but Valid</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>niakhar_hdss_cdm_Standard</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>nuhdss_cdm_Non-Standard but Valid</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>nuhdss_cdm_Standard</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>ouagadougou_hdss_cdm_Non-Standard but Valid</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>ouagadougou_hdss_cdm_Standard</t>
         </is>
@@ -31793,23 +31823,41 @@
         </is>
       </c>
       <c r="B2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C2">
         <v>2</v>
       </c>
       <c r="D2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E2">
         <v>2</v>
       </c>
       <c r="F2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G2">
         <v>2</v>
       </c>
+      <c r="H2">
+        <v>0</v>
+      </c>
+      <c r="I2">
+        <v>2</v>
+      </c>
+      <c r="J2">
+        <v>0</v>
+      </c>
+      <c r="K2">
+        <v>2</v>
+      </c>
+      <c r="L2">
+        <v>0</v>
+      </c>
+      <c r="M2">
+        <v>2</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -31818,22 +31866,40 @@
         </is>
       </c>
       <c r="B3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G3">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="H3">
+        <v>1</v>
+      </c>
+      <c r="I3">
+        <v>1</v>
+      </c>
+      <c r="J3">
+        <v>1</v>
+      </c>
+      <c r="K3">
+        <v>1</v>
+      </c>
+      <c r="L3">
+        <v>1</v>
+      </c>
+      <c r="M3">
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -31843,23 +31909,41 @@
         </is>
       </c>
       <c r="B4">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C4">
         <v>2</v>
       </c>
       <c r="D4">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E4">
         <v>2</v>
       </c>
       <c r="F4">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G4">
         <v>2</v>
       </c>
+      <c r="H4">
+        <v>0</v>
+      </c>
+      <c r="I4">
+        <v>2</v>
+      </c>
+      <c r="J4">
+        <v>0</v>
+      </c>
+      <c r="K4">
+        <v>2</v>
+      </c>
+      <c r="L4">
+        <v>0</v>
+      </c>
+      <c r="M4">
+        <v>2</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -31868,21 +31952,39 @@
         </is>
       </c>
       <c r="B5">
+        <v>0</v>
+      </c>
+      <c r="C5">
         <v>49</v>
       </c>
-      <c r="C5">
+      <c r="D5">
+        <v>0</v>
+      </c>
+      <c r="E5">
         <v>64</v>
       </c>
-      <c r="D5">
+      <c r="F5">
+        <v>0</v>
+      </c>
+      <c r="G5">
         <v>45</v>
       </c>
-      <c r="E5">
+      <c r="H5">
+        <v>0</v>
+      </c>
+      <c r="I5">
         <v>58</v>
       </c>
-      <c r="F5">
+      <c r="J5">
+        <v>0</v>
+      </c>
+      <c r="K5">
         <v>43</v>
       </c>
-      <c r="G5">
+      <c r="L5">
+        <v>0</v>
+      </c>
+      <c r="M5">
         <v>46</v>
       </c>
     </row>
@@ -31893,21 +31995,39 @@
         </is>
       </c>
       <c r="B6">
+        <v>0</v>
+      </c>
+      <c r="C6">
         <v>8</v>
       </c>
-      <c r="C6">
+      <c r="D6">
+        <v>0</v>
+      </c>
+      <c r="E6">
         <v>9</v>
       </c>
-      <c r="D6">
+      <c r="F6">
+        <v>0</v>
+      </c>
+      <c r="G6">
         <v>8</v>
       </c>
-      <c r="E6">
+      <c r="H6">
+        <v>0</v>
+      </c>
+      <c r="I6">
         <v>8</v>
       </c>
-      <c r="F6">
+      <c r="J6">
+        <v>0</v>
+      </c>
+      <c r="K6">
         <v>7</v>
       </c>
-      <c r="G6">
+      <c r="L6">
+        <v>0</v>
+      </c>
+      <c r="M6">
         <v>7</v>
       </c>
     </row>
@@ -31918,21 +32038,39 @@
         </is>
       </c>
       <c r="B7">
-        <v>21</v>
+        <v>6</v>
       </c>
       <c r="C7">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="D7">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="E7">
+        <v>15</v>
+      </c>
+      <c r="F7">
+        <v>6</v>
+      </c>
+      <c r="G7">
+        <v>13</v>
+      </c>
+      <c r="H7">
+        <v>0</v>
+      </c>
+      <c r="I7">
         <v>10</v>
       </c>
-      <c r="F7">
+      <c r="J7">
+        <v>0</v>
+      </c>
+      <c r="K7">
         <v>9</v>
       </c>
-      <c r="G7">
+      <c r="L7">
+        <v>0</v>
+      </c>
+      <c r="M7">
         <v>11</v>
       </c>
     </row>
@@ -31943,23 +32081,41 @@
         </is>
       </c>
       <c r="B8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C8">
         <v>1</v>
       </c>
       <c r="D8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E8">
         <v>1</v>
       </c>
       <c r="F8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G8">
         <v>1</v>
       </c>
+      <c r="H8">
+        <v>0</v>
+      </c>
+      <c r="I8">
+        <v>1</v>
+      </c>
+      <c r="J8">
+        <v>0</v>
+      </c>
+      <c r="K8">
+        <v>1</v>
+      </c>
+      <c r="L8">
+        <v>0</v>
+      </c>
+      <c r="M8">
+        <v>1</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -31968,23 +32124,41 @@
         </is>
       </c>
       <c r="B9">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C9">
         <v>2</v>
       </c>
       <c r="D9">
+        <v>0</v>
+      </c>
+      <c r="E9">
         <v>2</v>
       </c>
-      <c r="E9">
-        <v>3</v>
-      </c>
       <c r="F9">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G9">
         <v>2</v>
       </c>
+      <c r="H9">
+        <v>1</v>
+      </c>
+      <c r="I9">
+        <v>2</v>
+      </c>
+      <c r="J9">
+        <v>0</v>
+      </c>
+      <c r="K9">
+        <v>2</v>
+      </c>
+      <c r="L9">
+        <v>0</v>
+      </c>
+      <c r="M9">
+        <v>2</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -31993,23 +32167,41 @@
         </is>
       </c>
       <c r="B10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C10">
         <v>1</v>
       </c>
       <c r="D10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E10">
         <v>1</v>
       </c>
       <c r="F10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G10">
         <v>1</v>
       </c>
+      <c r="H10">
+        <v>0</v>
+      </c>
+      <c r="I10">
+        <v>1</v>
+      </c>
+      <c r="J10">
+        <v>0</v>
+      </c>
+      <c r="K10">
+        <v>1</v>
+      </c>
+      <c r="L10">
+        <v>0</v>
+      </c>
+      <c r="M10">
+        <v>1</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -32018,21 +32210,39 @@
         </is>
       </c>
       <c r="B11">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C11">
         <v>1</v>
       </c>
       <c r="D11">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E11">
         <v>1</v>
       </c>
       <c r="F11">
+        <v>0</v>
+      </c>
+      <c r="G11">
         <v>1</v>
       </c>
-      <c r="G11">
+      <c r="H11">
+        <v>0</v>
+      </c>
+      <c r="I11">
+        <v>1</v>
+      </c>
+      <c r="J11">
+        <v>0</v>
+      </c>
+      <c r="K11">
+        <v>1</v>
+      </c>
+      <c r="L11">
+        <v>0</v>
+      </c>
+      <c r="M11">
         <v>1</v>
       </c>
     </row>
